--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,6 +3386,1493 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118971467</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>460239</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6865118</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118970817</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>460261</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6864487</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118970882</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>460308</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6864558</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118970852</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>460285</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6864500</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118970995</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>460368</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6864629</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118971403</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>460250</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6865013</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118970916</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>460290</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6864536</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118971067</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>460363</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6864770</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118971510</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>460235</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6865172</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118970892</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>460325</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6864558</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118971628</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91412</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>460237</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6865171</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118970807</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>460246</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6864490</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118971311</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91077</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>760</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>460291</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6864922</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hittad i avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118970966</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>460368</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6864629</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -3388,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118971467</v>
+        <v>118971403</v>
       </c>
       <c r="B26" t="n">
-        <v>91780</v>
+        <v>91798</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3400,47 +3400,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Härjåsjön  (Härjåsjön ), Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460239</v>
+        <v>460250</v>
       </c>
       <c r="R26" t="n">
-        <v>6865118</v>
+        <v>6865013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3499,10 +3490,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118970817</v>
+        <v>118971628</v>
       </c>
       <c r="B27" t="n">
-        <v>91780</v>
+        <v>91412</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3515,21 +3506,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3539,13 +3530,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460261</v>
+        <v>460237</v>
       </c>
       <c r="R27" t="n">
-        <v>6864487</v>
+        <v>6865171</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3601,7 +3592,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118970882</v>
+        <v>118970892</v>
       </c>
       <c r="B28" t="n">
         <v>91780</v>
@@ -3636,7 +3627,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3650,7 +3641,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460308</v>
+        <v>460325</v>
       </c>
       <c r="R28" t="n">
         <v>6864558</v>
@@ -3712,10 +3703,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118970852</v>
+        <v>118971311</v>
       </c>
       <c r="B29" t="n">
-        <v>91780</v>
+        <v>91077</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,30 +3715,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3761,10 +3752,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460285</v>
+        <v>460291</v>
       </c>
       <c r="R29" t="n">
-        <v>6864500</v>
+        <v>6864922</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3797,6 +3788,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hittad i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,7 +3819,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118970995</v>
+        <v>118971067</v>
       </c>
       <c r="B30" t="n">
         <v>91780</v>
@@ -3856,26 +3852,17 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Härjåsjön  (Härjåsjön ), Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460368</v>
+        <v>460363</v>
       </c>
       <c r="R30" t="n">
-        <v>6864629</v>
+        <v>6864770</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3934,10 +3921,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118971403</v>
+        <v>118971467</v>
       </c>
       <c r="B31" t="n">
-        <v>91798</v>
+        <v>91780</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3946,38 +3933,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Härjåsjön  (Härjåsjön ), Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460250</v>
+        <v>460239</v>
       </c>
       <c r="R31" t="n">
-        <v>6865013</v>
+        <v>6865118</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118970916</v>
+        <v>118971510</v>
       </c>
       <c r="B32" t="n">
-        <v>91798</v>
+        <v>91780</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4048,25 +4044,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4076,10 +4072,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460290</v>
+        <v>460235</v>
       </c>
       <c r="R32" t="n">
-        <v>6864536</v>
+        <v>6865172</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4138,7 +4134,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118971067</v>
+        <v>118970852</v>
       </c>
       <c r="B33" t="n">
         <v>91780</v>
@@ -4171,17 +4167,26 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Härjåsjön  (Härjåsjön ), Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460363</v>
+        <v>460285</v>
       </c>
       <c r="R33" t="n">
-        <v>6864770</v>
+        <v>6864500</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4240,10 +4245,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118971510</v>
+        <v>118970966</v>
       </c>
       <c r="B34" t="n">
-        <v>91780</v>
+        <v>91798</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4252,25 +4257,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4285,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460235</v>
+        <v>460368</v>
       </c>
       <c r="R34" t="n">
-        <v>6865172</v>
+        <v>6864629</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4342,10 +4347,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118970892</v>
+        <v>118970916</v>
       </c>
       <c r="B35" t="n">
-        <v>91780</v>
+        <v>91798</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4354,47 +4359,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Härjåsjön  (Härjåsjön ), Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460325</v>
+        <v>460290</v>
       </c>
       <c r="R35" t="n">
-        <v>6864558</v>
+        <v>6864536</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4453,10 +4449,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118971628</v>
+        <v>118970817</v>
       </c>
       <c r="B36" t="n">
-        <v>91412</v>
+        <v>91780</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4469,21 +4465,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,13 +4489,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460237</v>
+        <v>460261</v>
       </c>
       <c r="R36" t="n">
-        <v>6865171</v>
+        <v>6864487</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4657,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118971311</v>
+        <v>118970882</v>
       </c>
       <c r="B38" t="n">
-        <v>91077</v>
+        <v>91780</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4669,25 +4665,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4706,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460291</v>
+        <v>460308</v>
       </c>
       <c r="R38" t="n">
-        <v>6864922</v>
+        <v>6864558</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4742,11 +4738,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hittad i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4773,10 +4764,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118970966</v>
+        <v>118970995</v>
       </c>
       <c r="B39" t="n">
-        <v>91798</v>
+        <v>91780</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4785,28 +4776,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Härjåsjön  (Härjåsjön ), Hjd</t>

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -3604,11 +3604,11 @@
         <v>118970817</v>
       </c>
       <c r="B28" t="n">
-        <v>91803</v>
+        <v>91998</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3637,7 +3637,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
@@ -3919,11 +3919,11 @@
         <v>118970852</v>
       </c>
       <c r="B31" t="n">
-        <v>91803</v>
+        <v>91998</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -3604,7 +3604,7 @@
         <v>118970817</v>
       </c>
       <c r="B28" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>118970852</v>
       </c>
       <c r="B31" t="n">
-        <v>91998</v>
+        <v>92012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -3604,7 +3604,7 @@
         <v>118970817</v>
       </c>
       <c r="B28" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>118970852</v>
       </c>
       <c r="B31" t="n">
-        <v>92012</v>
+        <v>92014</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -3604,7 +3604,7 @@
         <v>118970817</v>
       </c>
       <c r="B28" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>118970852</v>
       </c>
       <c r="B31" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -3604,7 +3604,7 @@
         <v>118970817</v>
       </c>
       <c r="B28" t="n">
-        <v>92015</v>
+        <v>92024</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>118970852</v>
       </c>
       <c r="B31" t="n">
-        <v>92015</v>
+        <v>92024</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 38354-2021 artfynd.xlsx
+++ b/artfynd/A 38354-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96205030</v>
+        <v>100711318</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Digerbäcken, Härjåsjön, Lillhärdal, Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460287.2877515909</v>
+        <v>460251</v>
       </c>
       <c r="R2" t="n">
-        <v>6864473.027424972</v>
+        <v>6864617</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar med mycel på och i anslutning till stig/färdväg</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Syrjälä</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100711285</v>
+        <v>100711319</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460059.8156610769</v>
+        <v>460287</v>
       </c>
       <c r="R3" t="n">
-        <v>6865157.950161108</v>
+        <v>6864665</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,19 +840,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,53 +869,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100711262</v>
+        <v>118971311</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460300.2726175658</v>
+        <v>460291</v>
       </c>
       <c r="R4" t="n">
-        <v>6864818.26706704</v>
+        <v>6864922</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +943,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hittad i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +968,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100711283</v>
+        <v>100711268</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460249.4347896811</v>
+        <v>460250</v>
       </c>
       <c r="R5" t="n">
-        <v>6864545.565035199</v>
+        <v>6864545</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,19 +1048,9 @@
           <t>2022-05-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,15 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100711264</v>
+        <v>102963245</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,37 +1088,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460281.3945901865</v>
+        <v>460342</v>
       </c>
       <c r="R6" t="n">
-        <v>6864655.926615504</v>
+        <v>6864596</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,22 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,27 +1163,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100711321</v>
+        <v>102963264</v>
       </c>
       <c r="B7" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,37 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460249.4347896811</v>
+        <v>460372</v>
       </c>
       <c r="R7" t="n">
-        <v>6864545.565035199</v>
+        <v>6864751</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,22 +1241,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,65 +1261,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100711282</v>
+        <v>102963138</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460211.3027450467</v>
+        <v>460288</v>
       </c>
       <c r="R8" t="n">
-        <v>6865119.902124813</v>
+        <v>6864483</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,22 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,27 +1359,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100711284</v>
+        <v>102963181</v>
       </c>
       <c r="B9" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,37 +1382,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460244.3252650601</v>
+        <v>460361</v>
       </c>
       <c r="R9" t="n">
-        <v>6864957.44221347</v>
+        <v>6864641</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,22 +1437,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,27 +1457,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100711265</v>
+        <v>102963197</v>
       </c>
       <c r="B10" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,37 +1480,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460288.6528065644</v>
+        <v>460349</v>
       </c>
       <c r="R10" t="n">
-        <v>6864792.958631675</v>
+        <v>6864767</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,22 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,27 +1555,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100711318</v>
+        <v>118970817</v>
       </c>
       <c r="B11" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,37 +1578,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460251.6903234392</v>
+        <v>460261</v>
       </c>
       <c r="R11" t="n">
-        <v>6864617.633973957</v>
+        <v>6864487</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1766,22 +1632,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,27 +1652,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100711319</v>
+        <v>118970852</v>
       </c>
       <c r="B12" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,37 +1675,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460287.1608893271</v>
+        <v>460285</v>
       </c>
       <c r="R12" t="n">
-        <v>6864664.812271135</v>
+        <v>6864500</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,22 +1738,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,27 +1758,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100711268</v>
+        <v>118970882</v>
       </c>
       <c r="B13" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,37 +1781,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>967</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>..., Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460249.4347896811</v>
+        <v>460308</v>
       </c>
       <c r="R13" t="n">
-        <v>6864545.565035199</v>
+        <v>6864558</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,22 +1844,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,66 +1864,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102962864</v>
+        <v>118970892</v>
       </c>
       <c r="B14" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460219.6078986617</v>
+        <v>460325</v>
       </c>
       <c r="R14" t="n">
-        <v>6865103.78656082</v>
+        <v>6864558</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,22 +1950,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,15 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102963181</v>
+        <v>118970995</v>
       </c>
       <c r="B15" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2178,21 +2010,29 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460361.443194225</v>
+        <v>460368</v>
       </c>
       <c r="R15" t="n">
-        <v>6864640.859446737</v>
+        <v>6864629</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,22 +2056,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,15 +2088,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102963138</v>
+        <v>118971023</v>
       </c>
       <c r="B16" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2292,20 +2117,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460288.3466638895</v>
+        <v>460376</v>
       </c>
       <c r="R16" t="n">
-        <v>6864482.910817255</v>
+        <v>6864737</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,22 +2153,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,15 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102963245</v>
+        <v>118971067</v>
       </c>
       <c r="B17" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,38 +2196,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460342.043670613</v>
+        <v>460363</v>
       </c>
       <c r="R17" t="n">
-        <v>6864595.849233164</v>
+        <v>6864770</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,22 +2250,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,54 +2282,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102963022</v>
+        <v>118971467</v>
       </c>
       <c r="B18" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>460241.1602503171</v>
+        <v>460239</v>
       </c>
       <c r="R18" t="n">
-        <v>6864483.460444622</v>
+        <v>6865118</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2555,22 +2356,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,15 +2388,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102963264</v>
+        <v>118971510</v>
       </c>
       <c r="B19" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,38 +2399,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>460372.160821597</v>
+        <v>460235</v>
       </c>
       <c r="R19" t="n">
-        <v>6864750.994415481</v>
+        <v>6865172</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2668,22 +2453,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,51 +2485,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102963005</v>
+        <v>96205030</v>
       </c>
       <c r="B20" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnberget Härjåsjön, Hjd</t>
+          <t>Digerbäcken, Härjåsjön, Lillhärdal, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460274.2126863243</v>
+        <v>460288</v>
       </c>
       <c r="R20" t="n">
-        <v>6864484.960277137</v>
+        <v>6864473</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,22 +2557,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar med mycel på och i anslutning till stig/färdväg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,33 +2576,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Syrjälä</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102963197</v>
+        <v>102962845</v>
       </c>
       <c r="B21" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,21 +2606,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2864,10 +2631,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460348.7501984098</v>
+        <v>460238</v>
       </c>
       <c r="R21" t="n">
-        <v>6864766.815604826</v>
+        <v>6865141</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,19 +2664,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,19 +2693,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102962845</v>
+        <v>102962864</v>
       </c>
       <c r="B22" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2977,10 +2729,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460237.9748427912</v>
+        <v>460220</v>
       </c>
       <c r="R22" t="n">
-        <v>6865141.263273752</v>
+        <v>6865104</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3010,19 +2762,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3052,16 +2794,11 @@
         <v>102962879</v>
       </c>
       <c r="B23" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3090,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>460248.0789009043</v>
+        <v>460248</v>
       </c>
       <c r="R23" t="n">
-        <v>6865077.07072281</v>
+        <v>6865077</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3123,19 +2860,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3162,19 +2889,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102962954</v>
+        <v>102962890</v>
       </c>
       <c r="B24" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3203,10 +2925,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>460360.5881106061</v>
+        <v>460255</v>
       </c>
       <c r="R24" t="n">
-        <v>6864607.885081832</v>
+        <v>6865015</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3236,19 +2958,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,19 +2987,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102962890</v>
+        <v>102962908</v>
       </c>
       <c r="B25" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3316,10 +3023,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>460254.8972899902</v>
+        <v>460377</v>
       </c>
       <c r="R25" t="n">
-        <v>6865014.328748026</v>
+        <v>6864653</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3349,19 +3056,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,19 +3085,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118970807</v>
+        <v>102962954</v>
       </c>
       <c r="B26" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3422,19 +3114,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>460246</v>
+        <v>460361</v>
       </c>
       <c r="R26" t="n">
-        <v>6864490</v>
+        <v>6864608</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3458,12 +3151,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,15 +3183,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118970995</v>
+        <v>102963005</v>
       </c>
       <c r="B27" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3506,46 +3194,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>460368</v>
+        <v>460274</v>
       </c>
       <c r="R27" t="n">
-        <v>6864629</v>
+        <v>6864485</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,12 +3249,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,15 +3281,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118970817</v>
+        <v>102963022</v>
       </c>
       <c r="B28" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,37 +3292,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härjåsjön , Härjåsjön , Hjd</t>
+          <t>Kvarnberget Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>460261</v>
+        <v>460241</v>
       </c>
       <c r="R28" t="n">
-        <v>6864487</v>
+        <v>6864483</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3671,12 +3347,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,15 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118971467</v>
+        <v>118970807</v>
       </c>
       <c r="B29" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,43 +3390,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>460239</v>
+        <v>460246</v>
       </c>
       <c r="R29" t="n">
-        <v>6865118</v>
+        <v>6864490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,15 +3476,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118971510</v>
+        <v>118970916</v>
       </c>
       <c r="B30" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,34 +3487,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>460235</v>
+        <v>460290</v>
       </c>
       <c r="R30" t="n">
-        <v>6865172</v>
+        <v>6864536</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3916,15 +3573,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118970852</v>
+        <v>118970966</v>
       </c>
       <c r="B31" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3932,43 +3584,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>460285</v>
+        <v>460368</v>
       </c>
       <c r="R31" t="n">
-        <v>6864500</v>
+        <v>6864629</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4027,15 +3670,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118970892</v>
+        <v>118971403</v>
       </c>
       <c r="B32" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,46 +3681,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>460325</v>
+        <v>460250</v>
       </c>
       <c r="R32" t="n">
-        <v>6864558</v>
+        <v>6865013</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4138,50 +3767,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118971403</v>
+        <v>118971628</v>
       </c>
       <c r="B33" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>Härjåsjön , Härjåsjön , Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>460250</v>
+        <v>460237</v>
       </c>
       <c r="R33" t="n">
-        <v>6865013</v>
+        <v>6865171</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,15 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118971628</v>
+        <v>100711262</v>
       </c>
       <c r="B34" t="n">
-        <v>91432</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,37 +3875,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4745</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>460237</v>
+        <v>460300</v>
       </c>
       <c r="R34" t="n">
-        <v>6865171</v>
+        <v>6864818</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4310,12 +3929,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4330,74 +3949,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118970882</v>
+        <v>100711282</v>
       </c>
       <c r="B35" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>460308</v>
+        <v>460212</v>
       </c>
       <c r="R35" t="n">
-        <v>6864558</v>
+        <v>6865120</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4421,12 +4026,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4441,65 +4046,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118970966</v>
+        <v>100711321</v>
       </c>
       <c r="B36" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>460368</v>
+        <v>460250</v>
       </c>
       <c r="R36" t="n">
-        <v>6864629</v>
+        <v>6864545</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4523,12 +4123,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4543,65 +4143,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118970916</v>
+        <v>100711283</v>
       </c>
       <c r="B37" t="n">
-        <v>91821</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460290</v>
+        <v>460250</v>
       </c>
       <c r="R37" t="n">
-        <v>6864536</v>
+        <v>6864545</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4625,12 +4220,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4645,74 +4240,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118971311</v>
+        <v>100711284</v>
       </c>
       <c r="B38" t="n">
-        <v>91097</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>460291</v>
+        <v>460245</v>
       </c>
       <c r="R38" t="n">
-        <v>6864922</v>
+        <v>6864957</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4736,17 +4317,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hittad i avverkningsanmälan.</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4761,27 +4337,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118971067</v>
+        <v>100711285</v>
       </c>
       <c r="B39" t="n">
-        <v>91803</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,37 +4360,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Härjåsjön  (Härjåsjön ), Hjd</t>
+          <t>..., Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460363</v>
+        <v>460060</v>
       </c>
       <c r="R39" t="n">
-        <v>6864770</v>
+        <v>6865158</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4843,12 +4414,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,15 +4434,209 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>100711264</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>460281</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6864656</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>100711265</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>..., Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>460288</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6864793</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-05-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
